--- a/data/APT_Tungsten_EU.xlsx
+++ b/data/APT_Tungsten_EU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mns4abt\CarbideForecastingApp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38470F85-6C61-48FA-BF6D-282F055FFF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCA31691-C3A1-46B5-8674-BBC7BED54CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_table" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="789">
   <si>
     <t>MaterialName</t>
   </si>
@@ -40,10 +40,13 @@
     <t>Tungsten APT 88.5% WO3 min cif Rotterdam and Baltimore duty-free, $/mtu WO3, mid price</t>
   </si>
   <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>USD/mtu WO3</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>USD/mtu WO3</t>
   </si>
   <si>
     <t>2026-09-25</t>
@@ -2390,7 +2393,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -2444,12 +2447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2800,34 +2798,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E783"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:E784"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="5" customWidth="1"/>
+    <col min="1" max="5" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="75" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2838,13 +2832,13 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2861,7 +2855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2872,13 +2866,13 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>2950</v>
+        <v>2800</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2895,7 +2889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2912,7 +2906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2929,7 +2923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2946,7 +2940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2957,13 +2951,13 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>3087.5</v>
+        <v>2950</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2980,7 +2974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2991,13 +2985,13 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>3139.5</v>
+        <v>3087.5</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -3014,7 +3008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -3031,7 +3025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -3042,13 +3036,13 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>3132.5</v>
+        <v>3139.5</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -3065,7 +3059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -3076,13 +3070,13 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>3075</v>
+        <v>3132.5</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3093,13 +3087,13 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>3055</v>
+        <v>3075</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -3110,13 +3104,13 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>3040</v>
+        <v>3055</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3133,7 +3127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3150,7 +3144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -3161,13 +3155,13 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>3140</v>
+        <v>3040</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -3184,7 +3178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3201,7 +3195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3218,7 +3212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3229,13 +3223,13 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>3060</v>
+        <v>3140</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3246,13 +3240,13 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>3044.5</v>
+        <v>3060</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3263,13 +3257,13 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>3040</v>
+        <v>3044.5</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -3280,13 +3274,13 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>2995</v>
+        <v>3040</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3297,13 +3291,13 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>2975</v>
+        <v>2995</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -3314,13 +3308,13 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>2650</v>
+        <v>2975</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -3331,13 +3325,13 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>2250</v>
+        <v>2650</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -3348,13 +3342,13 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>2097.5</v>
+        <v>2250</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -3365,13 +3359,13 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>1944</v>
+        <v>2097.5</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -3382,13 +3376,13 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>1775</v>
+        <v>1944</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -3399,13 +3393,13 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>1737.5</v>
+        <v>1775</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -3416,13 +3410,13 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>1375</v>
+        <v>1737.5</v>
       </c>
       <c r="E36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -3433,13 +3427,13 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>1249</v>
+        <v>1375</v>
       </c>
       <c r="E37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -3450,13 +3444,13 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>1202.5</v>
+        <v>1249</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3467,13 +3461,13 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>1018.5</v>
+        <v>1202.5</v>
       </c>
       <c r="E39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -3484,13 +3478,13 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>968.5</v>
+        <v>1018.5</v>
       </c>
       <c r="E40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -3501,13 +3495,13 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>920</v>
+        <v>968.5</v>
       </c>
       <c r="E41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -3518,13 +3512,13 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>862.5</v>
+        <v>920</v>
       </c>
       <c r="E42" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -3541,7 +3535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -3552,13 +3546,13 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>812.5</v>
+        <v>862.5</v>
       </c>
       <c r="E44" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -3569,13 +3563,13 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>770</v>
+        <v>812.5</v>
       </c>
       <c r="E45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -3586,13 +3580,13 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>757.5</v>
+        <v>770</v>
       </c>
       <c r="E46" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -3609,7 +3603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3620,13 +3614,13 @@
         <v>7</v>
       </c>
       <c r="D48">
-        <v>689.38</v>
+        <v>757.5</v>
       </c>
       <c r="E48" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -3637,13 +3631,13 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>673.75</v>
+        <v>689.38</v>
       </c>
       <c r="E49" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -3654,13 +3648,13 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>647.5</v>
+        <v>673.75</v>
       </c>
       <c r="E50" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -3677,7 +3671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -3688,13 +3682,13 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>642.5</v>
+        <v>647.5</v>
       </c>
       <c r="E52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -3705,13 +3699,13 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>635</v>
+        <v>642.5</v>
       </c>
       <c r="E53" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -3722,13 +3716,13 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="E54" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -3745,7 +3739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -3756,13 +3750,13 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E56" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -3773,13 +3767,13 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>597.5</v>
+        <v>610</v>
       </c>
       <c r="E57" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -3790,13 +3784,13 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>542.5</v>
+        <v>597.5</v>
       </c>
       <c r="E58" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -3807,13 +3801,13 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>520</v>
+        <v>542.5</v>
       </c>
       <c r="E59" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -3824,13 +3818,13 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>502.5</v>
+        <v>520</v>
       </c>
       <c r="E60" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -3841,13 +3835,13 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>495</v>
+        <v>502.5</v>
       </c>
       <c r="E61" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -3858,13 +3852,13 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E62" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -3875,13 +3869,13 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -3892,13 +3886,13 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="E64" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -3909,13 +3903,13 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>472.5</v>
+        <v>475</v>
       </c>
       <c r="E65" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -3932,7 +3926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -3943,13 +3937,13 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>462.5</v>
+        <v>472.5</v>
       </c>
       <c r="E67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -3966,7 +3960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -3977,13 +3971,13 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>452.5</v>
+        <v>462.5</v>
       </c>
       <c r="E69" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -3994,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>430</v>
+        <v>452.5</v>
       </c>
       <c r="E70" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -4017,7 +4011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -4028,13 +4022,13 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>427.5</v>
+        <v>430</v>
       </c>
       <c r="E72" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -4045,13 +4039,13 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>415</v>
+        <v>427.5</v>
       </c>
       <c r="E73" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -4068,7 +4062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -4079,13 +4073,13 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E75" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -4102,7 +4096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -4113,13 +4107,13 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E77" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -4130,13 +4124,13 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E78" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -4153,7 +4147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -4164,13 +4158,13 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E80" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -4187,7 +4181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -4198,13 +4192,13 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>357.5</v>
+        <v>360</v>
       </c>
       <c r="E82" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -4215,13 +4209,13 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>355</v>
+        <v>357.5</v>
       </c>
       <c r="E83" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -4232,13 +4226,13 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>352.5</v>
+        <v>355</v>
       </c>
       <c r="E84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -4249,13 +4243,13 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>345</v>
+        <v>352.5</v>
       </c>
       <c r="E85" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -4266,13 +4260,13 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>342.5</v>
+        <v>345</v>
       </c>
       <c r="E86" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -4289,7 +4283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -4306,7 +4300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -4323,7 +4317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -4340,7 +4334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -4351,13 +4345,13 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="E91" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -4368,13 +4362,13 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>332.5</v>
+        <v>337.5</v>
       </c>
       <c r="E92" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -4385,13 +4379,13 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>330</v>
+        <v>332.5</v>
       </c>
       <c r="E93" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -4408,7 +4402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -4425,7 +4419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -4436,13 +4430,13 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>331.5</v>
+        <v>330</v>
       </c>
       <c r="E96" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -4459,7 +4453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -4476,7 +4470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -4493,7 +4487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -4510,7 +4504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -4521,13 +4515,13 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>335</v>
+        <v>331.5</v>
       </c>
       <c r="E101" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -4544,7 +4538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -4561,7 +4555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -4578,7 +4572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -4595,7 +4589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -4612,7 +4606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -4629,7 +4623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -4646,7 +4640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -4663,7 +4657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -4680,7 +4674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4691,13 +4685,13 @@
         <v>7</v>
       </c>
       <c r="D111">
-        <v>332.5</v>
+        <v>335</v>
       </c>
       <c r="E111" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -4714,7 +4708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -4725,13 +4719,13 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>330</v>
+        <v>332.5</v>
       </c>
       <c r="E113" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -4748,7 +4742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -4765,7 +4759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -4782,7 +4776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -4793,13 +4787,13 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>332.5</v>
+        <v>330</v>
       </c>
       <c r="E117" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -4810,13 +4804,13 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>337.5</v>
+        <v>332.5</v>
       </c>
       <c r="E118" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -4827,13 +4821,13 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>345</v>
+        <v>337.5</v>
       </c>
       <c r="E119" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -4844,13 +4838,13 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>347.5</v>
+        <v>345</v>
       </c>
       <c r="E120" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -4867,7 +4861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -4884,7 +4878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -4901,7 +4895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -4918,7 +4912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -4929,13 +4923,13 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>341</v>
+        <v>347.5</v>
       </c>
       <c r="E125" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -4946,13 +4940,13 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>337.5</v>
+        <v>341</v>
       </c>
       <c r="E126" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -4969,7 +4963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -4980,13 +4974,13 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>332.5</v>
+        <v>337.5</v>
       </c>
       <c r="E128" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -4997,13 +4991,13 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>324.5</v>
+        <v>332.5</v>
       </c>
       <c r="E129" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -5014,13 +5008,13 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>315</v>
+        <v>324.5</v>
       </c>
       <c r="E130" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -5031,13 +5025,13 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>312.5</v>
+        <v>315</v>
       </c>
       <c r="E131" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -5048,13 +5042,13 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>316</v>
+        <v>312.5</v>
       </c>
       <c r="E132" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -5071,7 +5065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -5082,13 +5076,13 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>312.5</v>
+        <v>316</v>
       </c>
       <c r="E134" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -5105,7 +5099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -5122,7 +5116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -5139,7 +5133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -5156,7 +5150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -5173,7 +5167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -5190,7 +5184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -5207,7 +5201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -5224,7 +5218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -5241,7 +5235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -5258,7 +5252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -5275,7 +5269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -5292,7 +5286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -5309,7 +5303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -5326,7 +5320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -5343,7 +5337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -5360,7 +5354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -5377,7 +5371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -5394,7 +5388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -5405,13 +5399,13 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>315</v>
+        <v>312.5</v>
       </c>
       <c r="E153" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -5428,7 +5422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -5445,12 +5439,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C156" t="s">
         <v>7</v>
@@ -5462,7 +5456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -5479,7 +5473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -5496,7 +5490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -5513,7 +5507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -5530,7 +5524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -5547,7 +5541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -5564,7 +5558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -5581,7 +5575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -5598,7 +5592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -5609,13 +5603,13 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>317.5</v>
+        <v>315</v>
       </c>
       <c r="E165" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -5632,7 +5626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -5649,7 +5643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -5660,13 +5654,13 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>320</v>
+        <v>317.5</v>
       </c>
       <c r="E168" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -5683,7 +5677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -5700,7 +5694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>5</v>
       </c>
@@ -5717,7 +5711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>5</v>
       </c>
@@ -5728,13 +5722,13 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>322.5</v>
+        <v>320</v>
       </c>
       <c r="E172" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -5745,13 +5739,13 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>327.5</v>
+        <v>322.5</v>
       </c>
       <c r="E173" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -5768,7 +5762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5785,7 +5779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -5802,7 +5796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -5819,7 +5813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -5836,7 +5830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -5853,7 +5847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -5870,7 +5864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -5887,7 +5881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -5904,7 +5898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -5921,7 +5915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -5938,7 +5932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -5955,7 +5949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>5</v>
       </c>
@@ -5966,13 +5960,13 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>335</v>
+        <v>327.5</v>
       </c>
       <c r="E186" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -5983,13 +5977,13 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>336.5</v>
+        <v>335</v>
       </c>
       <c r="E187" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -6000,13 +5994,13 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>336.4</v>
+        <v>336.5</v>
       </c>
       <c r="E188" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -6017,13 +6011,13 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>341.5</v>
+        <v>336.4</v>
       </c>
       <c r="E189" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -6034,13 +6028,13 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>343.5</v>
+        <v>341.5</v>
       </c>
       <c r="E190" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -6057,7 +6051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -6074,7 +6068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -6085,13 +6079,13 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>342.5</v>
+        <v>343.5</v>
       </c>
       <c r="E193" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -6108,7 +6102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -6119,13 +6113,13 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="E195" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -6136,13 +6130,13 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>336.5</v>
+        <v>337.5</v>
       </c>
       <c r="E196" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -6159,7 +6153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -6170,13 +6164,13 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>335</v>
+        <v>336.5</v>
       </c>
       <c r="E198" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>5</v>
       </c>
@@ -6193,7 +6187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -6210,7 +6204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -6227,7 +6221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -6244,7 +6238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -6255,13 +6249,13 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E203" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -6272,13 +6266,13 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E204" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -6295,7 +6289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>5</v>
       </c>
@@ -6306,13 +6300,13 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>337.5</v>
+        <v>335</v>
       </c>
       <c r="E206" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -6329,7 +6323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>5</v>
       </c>
@@ -6346,7 +6340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -6363,7 +6357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -6380,7 +6374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -6397,7 +6391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -6414,7 +6408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>5</v>
       </c>
@@ -6431,7 +6425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>5</v>
       </c>
@@ -6448,7 +6442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -6459,13 +6453,13 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>342.5</v>
+        <v>337.5</v>
       </c>
       <c r="E215" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>5</v>
       </c>
@@ -6482,7 +6476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -6499,7 +6493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -6516,7 +6510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -6533,7 +6527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -6550,7 +6544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -6567,7 +6561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -6584,7 +6578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -6601,7 +6595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -6612,13 +6606,13 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>345</v>
+        <v>342.5</v>
       </c>
       <c r="E224" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -6635,7 +6629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -6646,13 +6640,13 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>346.5</v>
+        <v>345</v>
       </c>
       <c r="E226" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -6669,7 +6663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -6680,13 +6674,13 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>347.5</v>
+        <v>346.5</v>
       </c>
       <c r="E228" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -6703,7 +6697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -6720,7 +6714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -6731,13 +6725,13 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>348</v>
+        <v>347.5</v>
       </c>
       <c r="E231" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -6754,7 +6748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -6771,7 +6765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -6782,13 +6776,13 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>350.5</v>
+        <v>348</v>
       </c>
       <c r="E234" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -6799,13 +6793,13 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>349.5</v>
+        <v>350.5</v>
       </c>
       <c r="E235" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -6816,13 +6810,13 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>352.5</v>
+        <v>349.5</v>
       </c>
       <c r="E236" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -6839,7 +6833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>5</v>
       </c>
@@ -6850,13 +6844,13 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>353.5</v>
+        <v>352.5</v>
       </c>
       <c r="E238" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -6867,13 +6861,13 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>349</v>
+        <v>353.5</v>
       </c>
       <c r="E239" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -6890,7 +6884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -6901,13 +6895,13 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>348.5</v>
+        <v>349</v>
       </c>
       <c r="E241" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>5</v>
       </c>
@@ -6924,7 +6918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -6935,13 +6929,13 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>340</v>
+        <v>348.5</v>
       </c>
       <c r="E243" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>5</v>
       </c>
@@ -6952,13 +6946,13 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>342.5</v>
+        <v>340</v>
       </c>
       <c r="E244" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -6969,13 +6963,13 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>340</v>
+        <v>342.5</v>
       </c>
       <c r="E245" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -6986,13 +6980,13 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>336.5</v>
+        <v>340</v>
       </c>
       <c r="E246" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -7009,7 +7003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -7020,13 +7014,13 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>332.5</v>
+        <v>336.5</v>
       </c>
       <c r="E248" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -7037,13 +7031,13 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>328</v>
+        <v>332.5</v>
       </c>
       <c r="E249" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>5</v>
       </c>
@@ -7054,13 +7048,13 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>325.5</v>
+        <v>328</v>
       </c>
       <c r="E250" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>5</v>
       </c>
@@ -7071,13 +7065,13 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>322.5</v>
+        <v>325.5</v>
       </c>
       <c r="E251" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -7094,7 +7088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -7111,7 +7105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>5</v>
       </c>
@@ -7128,7 +7122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -7145,7 +7139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -7162,7 +7156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>5</v>
       </c>
@@ -7179,7 +7173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>5</v>
       </c>
@@ -7196,7 +7190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -7213,7 +7207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>5</v>
       </c>
@@ -7230,7 +7224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>5</v>
       </c>
@@ -7247,7 +7241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>5</v>
       </c>
@@ -7258,13 +7252,13 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>317.5</v>
+        <v>322.5</v>
       </c>
       <c r="E262" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>5</v>
       </c>
@@ -7281,7 +7275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -7298,7 +7292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>5</v>
       </c>
@@ -7309,13 +7303,13 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>315</v>
+        <v>317.5</v>
       </c>
       <c r="E265" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>5</v>
       </c>
@@ -7332,7 +7326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -7343,13 +7337,13 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>312.5</v>
+        <v>315</v>
       </c>
       <c r="E267" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -7366,7 +7360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -7383,7 +7377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>5</v>
       </c>
@@ -7400,7 +7394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>5</v>
       </c>
@@ -7417,7 +7411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>5</v>
       </c>
@@ -7428,13 +7422,13 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>311.5</v>
+        <v>312.5</v>
       </c>
       <c r="E272" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -7445,13 +7439,13 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>302.5</v>
+        <v>311.5</v>
       </c>
       <c r="E273" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -7462,13 +7456,13 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>292.5</v>
+        <v>302.5</v>
       </c>
       <c r="E274" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -7479,13 +7473,13 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>289.5</v>
+        <v>292.5</v>
       </c>
       <c r="E275" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>5</v>
       </c>
@@ -7502,7 +7496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -7513,13 +7507,13 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>284</v>
+        <v>289.5</v>
       </c>
       <c r="E277" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -7530,13 +7524,13 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>280.5</v>
+        <v>284</v>
       </c>
       <c r="E278" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>5</v>
       </c>
@@ -7547,13 +7541,13 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>275.5</v>
+        <v>280.5</v>
       </c>
       <c r="E279" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>5</v>
       </c>
@@ -7564,13 +7558,13 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>275</v>
+        <v>275.5</v>
       </c>
       <c r="E280" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>5</v>
       </c>
@@ -7587,7 +7581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -7598,13 +7592,13 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E282" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>5</v>
       </c>
@@ -7621,7 +7615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>5</v>
       </c>
@@ -7638,7 +7632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>5</v>
       </c>
@@ -7655,7 +7649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>5</v>
       </c>
@@ -7672,7 +7666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>5</v>
       </c>
@@ -7689,7 +7683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>5</v>
       </c>
@@ -7706,7 +7700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>5</v>
       </c>
@@ -7723,7 +7717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>5</v>
       </c>
@@ -7740,7 +7734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -7757,7 +7751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>5</v>
       </c>
@@ -7768,13 +7762,13 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>272.5</v>
+        <v>274</v>
       </c>
       <c r="E292" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>5</v>
       </c>
@@ -7785,13 +7779,13 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>271.5</v>
+        <v>272.5</v>
       </c>
       <c r="E293" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>5</v>
       </c>
@@ -7802,13 +7796,13 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>265.5</v>
+        <v>271.5</v>
       </c>
       <c r="E294" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>5</v>
       </c>
@@ -7819,13 +7813,13 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>262.5</v>
+        <v>265.5</v>
       </c>
       <c r="E295" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>5</v>
       </c>
@@ -7836,13 +7830,13 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>252.5</v>
+        <v>262.5</v>
       </c>
       <c r="E296" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>5</v>
       </c>
@@ -7859,7 +7853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>5</v>
       </c>
@@ -7876,7 +7870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>5</v>
       </c>
@@ -7887,13 +7881,13 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>247.5</v>
+        <v>252.5</v>
       </c>
       <c r="E299" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -7904,13 +7898,13 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>242.5</v>
+        <v>247.5</v>
       </c>
       <c r="E300" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -7921,13 +7915,13 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>237.5</v>
+        <v>242.5</v>
       </c>
       <c r="E301" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>5</v>
       </c>
@@ -7944,7 +7938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>5</v>
       </c>
@@ -7955,13 +7949,13 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>232.5</v>
+        <v>237.5</v>
       </c>
       <c r="E303" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>5</v>
       </c>
@@ -7978,7 +7972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>5</v>
       </c>
@@ -7995,7 +7989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>5</v>
       </c>
@@ -8006,13 +8000,13 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>225</v>
+        <v>232.5</v>
       </c>
       <c r="E306" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>5</v>
       </c>
@@ -8023,13 +8017,13 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>222.5</v>
+        <v>225</v>
       </c>
       <c r="E307" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>5</v>
       </c>
@@ -8046,7 +8040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -8063,7 +8057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>5</v>
       </c>
@@ -8080,7 +8074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>5</v>
       </c>
@@ -8097,7 +8091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>5</v>
       </c>
@@ -8114,7 +8108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -8131,7 +8125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>5</v>
       </c>
@@ -8142,13 +8136,13 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>216</v>
+        <v>222.5</v>
       </c>
       <c r="E314" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>5</v>
       </c>
@@ -8165,7 +8159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>5</v>
       </c>
@@ -8176,13 +8170,13 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>222.5</v>
+        <v>216</v>
       </c>
       <c r="E316" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>5</v>
       </c>
@@ -8199,7 +8193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -8216,7 +8210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>5</v>
       </c>
@@ -8233,7 +8227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -8244,13 +8238,13 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>216</v>
+        <v>222.5</v>
       </c>
       <c r="E320" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>5</v>
       </c>
@@ -8261,13 +8255,13 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>212.5</v>
+        <v>216</v>
       </c>
       <c r="E321" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>5</v>
       </c>
@@ -8278,13 +8272,13 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>207.5</v>
+        <v>212.5</v>
       </c>
       <c r="E322" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>5</v>
       </c>
@@ -8301,7 +8295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -8318,7 +8312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>5</v>
       </c>
@@ -8335,7 +8329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>5</v>
       </c>
@@ -8352,7 +8346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -8369,7 +8363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>5</v>
       </c>
@@ -8380,13 +8374,13 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>210</v>
+        <v>207.5</v>
       </c>
       <c r="E328" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>5</v>
       </c>
@@ -8403,7 +8397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>5</v>
       </c>
@@ -8420,7 +8414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>5</v>
       </c>
@@ -8437,7 +8431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>5</v>
       </c>
@@ -8448,13 +8442,13 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E332" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>5</v>
       </c>
@@ -8471,7 +8465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>5</v>
       </c>
@@ -8488,7 +8482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>5</v>
       </c>
@@ -8505,7 +8499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -8516,13 +8510,13 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E336" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>5</v>
       </c>
@@ -8533,13 +8527,13 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E337" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>5</v>
       </c>
@@ -8556,7 +8550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>5</v>
       </c>
@@ -8573,7 +8567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>5</v>
       </c>
@@ -8584,13 +8578,13 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>242.5</v>
+        <v>220</v>
       </c>
       <c r="E340" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>5</v>
       </c>
@@ -8607,7 +8601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>5</v>
       </c>
@@ -8624,7 +8618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>5</v>
       </c>
@@ -8641,7 +8635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>5</v>
       </c>
@@ -8658,7 +8652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -8675,7 +8669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>5</v>
       </c>
@@ -8692,7 +8686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>5</v>
       </c>
@@ -8709,7 +8703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>5</v>
       </c>
@@ -8726,7 +8720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>5</v>
       </c>
@@ -8743,7 +8737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>5</v>
       </c>
@@ -8760,7 +8754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>5</v>
       </c>
@@ -8771,13 +8765,13 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>240</v>
+        <v>242.5</v>
       </c>
       <c r="E351" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>5</v>
       </c>
@@ -8794,7 +8788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>5</v>
       </c>
@@ -8811,7 +8805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -8828,7 +8822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>5</v>
       </c>
@@ -8845,7 +8839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>5</v>
       </c>
@@ -8862,7 +8856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>5</v>
       </c>
@@ -8879,7 +8873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>5</v>
       </c>
@@ -8896,7 +8890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>5</v>
       </c>
@@ -8907,13 +8901,13 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>237.5</v>
+        <v>240</v>
       </c>
       <c r="E359" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>5</v>
       </c>
@@ -8924,13 +8918,13 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>235</v>
+        <v>237.5</v>
       </c>
       <c r="E360" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>5</v>
       </c>
@@ -8947,7 +8941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>5</v>
       </c>
@@ -8964,7 +8958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -8981,7 +8975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>5</v>
       </c>
@@ -8998,7 +8992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>5</v>
       </c>
@@ -9015,7 +9009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>5</v>
       </c>
@@ -9032,7 +9026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>5</v>
       </c>
@@ -9049,7 +9043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>5</v>
       </c>
@@ -9060,13 +9054,13 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E368" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>5</v>
       </c>
@@ -9083,7 +9077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>5</v>
       </c>
@@ -9094,13 +9088,13 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E370" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>5</v>
       </c>
@@ -9117,7 +9111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -9134,7 +9128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>5</v>
       </c>
@@ -9151,7 +9145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>5</v>
       </c>
@@ -9168,7 +9162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>5</v>
       </c>
@@ -9179,13 +9173,13 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E375" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>5</v>
       </c>
@@ -9202,7 +9196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>5</v>
       </c>
@@ -9213,13 +9207,13 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>217.5</v>
+        <v>205</v>
       </c>
       <c r="E377" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>5</v>
       </c>
@@ -9236,7 +9230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>5</v>
       </c>
@@ -9253,7 +9247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>5</v>
       </c>
@@ -9270,7 +9264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -9281,13 +9275,13 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>236</v>
+        <v>217.5</v>
       </c>
       <c r="E381" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>5</v>
       </c>
@@ -9298,13 +9292,13 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>252.5</v>
+        <v>236</v>
       </c>
       <c r="E382" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>5</v>
       </c>
@@ -9321,7 +9315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>5</v>
       </c>
@@ -9332,13 +9326,13 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>260</v>
+        <v>252.5</v>
       </c>
       <c r="E384" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>5</v>
       </c>
@@ -9349,13 +9343,13 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E385" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>5</v>
       </c>
@@ -9372,7 +9366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>5</v>
       </c>
@@ -9383,13 +9377,13 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E387" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>5</v>
       </c>
@@ -9406,7 +9400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>5</v>
       </c>
@@ -9423,7 +9417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -9440,7 +9434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>5</v>
       </c>
@@ -9457,7 +9451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>5</v>
       </c>
@@ -9468,13 +9462,13 @@
         <v>7</v>
       </c>
       <c r="D392">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E392" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>5</v>
       </c>
@@ -9491,7 +9485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>5</v>
       </c>
@@ -9508,7 +9502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>5</v>
       </c>
@@ -9519,13 +9513,13 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>276.5</v>
+        <v>276</v>
       </c>
       <c r="E395" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>5</v>
       </c>
@@ -9542,7 +9536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>5</v>
       </c>
@@ -9559,7 +9553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>5</v>
       </c>
@@ -9576,7 +9570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -9587,13 +9581,13 @@
         <v>7</v>
       </c>
       <c r="D399">
-        <v>275</v>
+        <v>276.5</v>
       </c>
       <c r="E399" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>5</v>
       </c>
@@ -9604,13 +9598,13 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E400" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>5</v>
       </c>
@@ -9621,13 +9615,13 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E401" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>5</v>
       </c>
@@ -9644,7 +9638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>5</v>
       </c>
@@ -9661,7 +9655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>5</v>
       </c>
@@ -9678,7 +9672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>5</v>
       </c>
@@ -9695,7 +9689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>5</v>
       </c>
@@ -9712,7 +9706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>5</v>
       </c>
@@ -9723,13 +9717,13 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E407" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>5</v>
       </c>
@@ -9740,13 +9734,13 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>277.5</v>
+        <v>275</v>
       </c>
       <c r="E408" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>5</v>
       </c>
@@ -9763,7 +9757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>5</v>
       </c>
@@ -9774,13 +9768,13 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>282.5</v>
+        <v>277.5</v>
       </c>
       <c r="E410" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>5</v>
       </c>
@@ -9797,7 +9791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>5</v>
       </c>
@@ -9808,13 +9802,13 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>285</v>
+        <v>282.5</v>
       </c>
       <c r="E412" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>5</v>
       </c>
@@ -9831,7 +9825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>5</v>
       </c>
@@ -9848,7 +9842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>5</v>
       </c>
@@ -9865,7 +9859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>5</v>
       </c>
@@ -9882,7 +9876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -9899,7 +9893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>5</v>
       </c>
@@ -9916,7 +9910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>5</v>
       </c>
@@ -9927,13 +9921,13 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>282.5</v>
+        <v>285</v>
       </c>
       <c r="E419" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>5</v>
       </c>
@@ -9950,7 +9944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>5</v>
       </c>
@@ -9967,7 +9961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>5</v>
       </c>
@@ -9984,7 +9978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>5</v>
       </c>
@@ -10001,7 +9995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>5</v>
       </c>
@@ -10018,7 +10012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>5</v>
       </c>
@@ -10035,7 +10029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>5</v>
       </c>
@@ -10046,13 +10040,13 @@
         <v>7</v>
       </c>
       <c r="D426">
-        <v>290</v>
+        <v>282.5</v>
       </c>
       <c r="E426" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>5</v>
       </c>
@@ -10063,13 +10057,13 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>307.5</v>
+        <v>290</v>
       </c>
       <c r="E427" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>5</v>
       </c>
@@ -10086,7 +10080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>5</v>
       </c>
@@ -10097,13 +10091,13 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>322.5</v>
+        <v>307.5</v>
       </c>
       <c r="E429" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>5</v>
       </c>
@@ -10114,13 +10108,13 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>326.5</v>
+        <v>322.5</v>
       </c>
       <c r="E430" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>5</v>
       </c>
@@ -10131,13 +10125,13 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>337</v>
+        <v>326.5</v>
       </c>
       <c r="E431" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>5</v>
       </c>
@@ -10148,13 +10142,13 @@
         <v>7</v>
       </c>
       <c r="D432">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E432" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>5</v>
       </c>
@@ -10165,13 +10159,13 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>346.5</v>
+        <v>342</v>
       </c>
       <c r="E433" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>5</v>
       </c>
@@ -10182,13 +10176,13 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>351.5</v>
+        <v>346.5</v>
       </c>
       <c r="E434" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -10199,13 +10193,13 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>352</v>
+        <v>351.5</v>
       </c>
       <c r="E435" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>5</v>
       </c>
@@ -10222,7 +10216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>5</v>
       </c>
@@ -10233,13 +10227,13 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>348.5</v>
+        <v>352</v>
       </c>
       <c r="E437" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>5</v>
       </c>
@@ -10250,13 +10244,13 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>344.5</v>
+        <v>348.5</v>
       </c>
       <c r="E438" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>5</v>
       </c>
@@ -10273,7 +10267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>5</v>
       </c>
@@ -10284,13 +10278,13 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>342.5</v>
+        <v>344.5</v>
       </c>
       <c r="E440" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>5</v>
       </c>
@@ -10301,13 +10295,13 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="E441" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>5</v>
       </c>
@@ -10318,13 +10312,13 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>331.5</v>
+        <v>337.5</v>
       </c>
       <c r="E442" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>5</v>
       </c>
@@ -10341,7 +10335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -10352,13 +10346,13 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>326.5</v>
+        <v>331.5</v>
       </c>
       <c r="E444" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>5</v>
       </c>
@@ -10369,13 +10363,13 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>325.5</v>
+        <v>326.5</v>
       </c>
       <c r="E445" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>5</v>
       </c>
@@ -10386,13 +10380,13 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>327.5</v>
+        <v>325.5</v>
       </c>
       <c r="E446" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>5</v>
       </c>
@@ -10403,13 +10397,13 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>329.5</v>
+        <v>327.5</v>
       </c>
       <c r="E447" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>5</v>
       </c>
@@ -10426,7 +10420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>5</v>
       </c>
@@ -10443,7 +10437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>5</v>
       </c>
@@ -10454,13 +10448,13 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>327.5</v>
+        <v>329.5</v>
       </c>
       <c r="E450" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -10471,13 +10465,13 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>326</v>
+        <v>327.5</v>
       </c>
       <c r="E451" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>5</v>
       </c>
@@ -10488,13 +10482,13 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>322.5</v>
+        <v>326</v>
       </c>
       <c r="E452" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>5</v>
       </c>
@@ -10505,13 +10499,13 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>322</v>
+        <v>322.5</v>
       </c>
       <c r="E453" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>5</v>
       </c>
@@ -10528,7 +10522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>5</v>
       </c>
@@ -10539,13 +10533,13 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E455" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>5</v>
       </c>
@@ -10556,13 +10550,13 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>317.5</v>
+        <v>321</v>
       </c>
       <c r="E456" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>5</v>
       </c>
@@ -10573,13 +10567,13 @@
         <v>7</v>
       </c>
       <c r="D457">
-        <v>316.5</v>
+        <v>317.5</v>
       </c>
       <c r="E457" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>5</v>
       </c>
@@ -10590,13 +10584,13 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>314</v>
+        <v>316.5</v>
       </c>
       <c r="E458" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>5</v>
       </c>
@@ -10607,13 +10601,13 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>312.5</v>
+        <v>314</v>
       </c>
       <c r="E459" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>5</v>
       </c>
@@ -10624,13 +10618,13 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>297.5</v>
+        <v>312.5</v>
       </c>
       <c r="E460" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>5</v>
       </c>
@@ -10647,7 +10641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>5</v>
       </c>
@@ -10664,7 +10658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>5</v>
       </c>
@@ -10675,13 +10669,13 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>296.5</v>
+        <v>297.5</v>
       </c>
       <c r="E463" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>5</v>
       </c>
@@ -10692,13 +10686,13 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>295.5</v>
+        <v>296.5</v>
       </c>
       <c r="E464" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>5</v>
       </c>
@@ -10709,13 +10703,13 @@
         <v>7</v>
       </c>
       <c r="D465">
-        <v>290</v>
+        <v>295.5</v>
       </c>
       <c r="E465" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>5</v>
       </c>
@@ -10726,13 +10720,13 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="E466" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>5</v>
       </c>
@@ -10743,13 +10737,13 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E467" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>5</v>
       </c>
@@ -10760,13 +10754,13 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E468" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>5</v>
       </c>
@@ -10783,7 +10777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>5</v>
       </c>
@@ -10794,13 +10788,13 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>282.5</v>
+        <v>280</v>
       </c>
       <c r="E470" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -10817,7 +10811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>5</v>
       </c>
@@ -10828,13 +10822,13 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>287.5</v>
+        <v>282.5</v>
       </c>
       <c r="E472" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>5</v>
       </c>
@@ -10845,13 +10839,13 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>297.5</v>
+        <v>287.5</v>
       </c>
       <c r="E473" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>5</v>
       </c>
@@ -10862,13 +10856,13 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>307.5</v>
+        <v>297.5</v>
       </c>
       <c r="E474" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>5</v>
       </c>
@@ -10879,13 +10873,13 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>322.5</v>
+        <v>307.5</v>
       </c>
       <c r="E475" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>5</v>
       </c>
@@ -10902,7 +10896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>5</v>
       </c>
@@ -10913,13 +10907,13 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>292.5</v>
+        <v>322.5</v>
       </c>
       <c r="E477" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>5</v>
       </c>
@@ -10930,13 +10924,13 @@
         <v>7</v>
       </c>
       <c r="D478">
-        <v>272</v>
+        <v>292.5</v>
       </c>
       <c r="E478" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>5</v>
       </c>
@@ -10947,13 +10941,13 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="E479" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>5</v>
       </c>
@@ -10964,13 +10958,13 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E480" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>5</v>
       </c>
@@ -10981,13 +10975,13 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E481" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>5</v>
       </c>
@@ -10998,13 +10992,13 @@
         <v>7</v>
       </c>
       <c r="D482">
-        <v>232.5</v>
+        <v>244</v>
       </c>
       <c r="E482" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>5</v>
       </c>
@@ -11015,13 +11009,13 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>228.5</v>
+        <v>232.5</v>
       </c>
       <c r="E483" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>5</v>
       </c>
@@ -11032,13 +11026,13 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>222</v>
+        <v>228.5</v>
       </c>
       <c r="E484" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>5</v>
       </c>
@@ -11049,13 +11043,13 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>218.5</v>
+        <v>222</v>
       </c>
       <c r="E485" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>5</v>
       </c>
@@ -11066,13 +11060,13 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>217</v>
+        <v>218.5</v>
       </c>
       <c r="E486" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>5</v>
       </c>
@@ -11083,13 +11077,13 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E487" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>5</v>
       </c>
@@ -11100,13 +11094,13 @@
         <v>7</v>
       </c>
       <c r="D488">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E488" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -11123,7 +11117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>5</v>
       </c>
@@ -11134,13 +11128,13 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>222.5</v>
+        <v>223</v>
       </c>
       <c r="E490" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>5</v>
       </c>
@@ -11157,7 +11151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>5</v>
       </c>
@@ -11168,13 +11162,13 @@
         <v>7</v>
       </c>
       <c r="D492">
-        <v>220</v>
+        <v>222.5</v>
       </c>
       <c r="E492" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>5</v>
       </c>
@@ -11185,13 +11179,13 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E493" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>5</v>
       </c>
@@ -11202,13 +11196,13 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>214.5</v>
+        <v>217</v>
       </c>
       <c r="E494" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>5</v>
       </c>
@@ -11219,13 +11213,13 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>215.5</v>
+        <v>214.5</v>
       </c>
       <c r="E495" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>5</v>
       </c>
@@ -11236,13 +11230,13 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>212</v>
+        <v>215.5</v>
       </c>
       <c r="E496" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>5</v>
       </c>
@@ -11253,13 +11247,13 @@
         <v>7</v>
       </c>
       <c r="D497">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E497" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>5</v>
       </c>
@@ -11276,7 +11270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>5</v>
       </c>
@@ -11287,13 +11281,13 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E499" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>5</v>
       </c>
@@ -11304,13 +11298,13 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E500" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>5</v>
       </c>
@@ -11321,13 +11315,13 @@
         <v>7</v>
       </c>
       <c r="D501">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E501" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>5</v>
       </c>
@@ -11338,13 +11332,13 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>214.5</v>
+        <v>212</v>
       </c>
       <c r="E502" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>5</v>
       </c>
@@ -11355,13 +11349,13 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>213.5</v>
+        <v>214.5</v>
       </c>
       <c r="E503" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>5</v>
       </c>
@@ -11372,13 +11366,13 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>202.5</v>
+        <v>213.5</v>
       </c>
       <c r="E504" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>5</v>
       </c>
@@ -11389,13 +11383,13 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>200</v>
+        <v>202.5</v>
       </c>
       <c r="E505" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>5</v>
       </c>
@@ -11406,13 +11400,13 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>200.5</v>
+        <v>200</v>
       </c>
       <c r="E506" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>5</v>
       </c>
@@ -11429,7 +11423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>5</v>
       </c>
@@ -11440,13 +11434,13 @@
         <v>7</v>
       </c>
       <c r="D508">
-        <v>196.75</v>
+        <v>200.5</v>
       </c>
       <c r="E508" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>5</v>
       </c>
@@ -11457,13 +11451,13 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>195.25</v>
+        <v>196.75</v>
       </c>
       <c r="E509" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>5</v>
       </c>
@@ -11480,7 +11474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>5</v>
       </c>
@@ -11491,13 +11485,13 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>192.5</v>
+        <v>195.25</v>
       </c>
       <c r="E511" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>5</v>
       </c>
@@ -11514,7 +11508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>5</v>
       </c>
@@ -11531,7 +11525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>5</v>
       </c>
@@ -11548,7 +11542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>5</v>
       </c>
@@ -11559,13 +11553,13 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>191</v>
+        <v>192.5</v>
       </c>
       <c r="E515" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -11576,13 +11570,13 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E516" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>5</v>
       </c>
@@ -11593,13 +11587,13 @@
         <v>7</v>
       </c>
       <c r="D517">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E517" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>5</v>
       </c>
@@ -11610,13 +11604,13 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>200.5</v>
+        <v>193</v>
       </c>
       <c r="E518" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>5</v>
       </c>
@@ -11633,7 +11627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>5</v>
       </c>
@@ -11644,13 +11638,13 @@
         <v>7</v>
       </c>
       <c r="D520">
-        <v>201.5</v>
+        <v>200.5</v>
       </c>
       <c r="E520" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -11661,13 +11655,13 @@
         <v>7</v>
       </c>
       <c r="D521">
-        <v>197</v>
+        <v>201.5</v>
       </c>
       <c r="E521" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>5</v>
       </c>
@@ -11678,13 +11672,13 @@
         <v>7</v>
       </c>
       <c r="D522">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E522" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>5</v>
       </c>
@@ -11695,13 +11689,13 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>193.5</v>
+        <v>194</v>
       </c>
       <c r="E523" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>5</v>
       </c>
@@ -11712,13 +11706,13 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>190</v>
+        <v>193.5</v>
       </c>
       <c r="E524" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>5</v>
       </c>
@@ -11735,7 +11729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>5</v>
       </c>
@@ -11752,7 +11746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>5</v>
       </c>
@@ -11769,7 +11763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>5</v>
       </c>
@@ -11786,7 +11780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>5</v>
       </c>
@@ -11803,7 +11797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>5</v>
       </c>
@@ -11820,7 +11814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>5</v>
       </c>
@@ -11831,13 +11825,13 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>192.5</v>
+        <v>190</v>
       </c>
       <c r="E531" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>5</v>
       </c>
@@ -11854,7 +11848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>5</v>
       </c>
@@ -11865,13 +11859,13 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>195</v>
+        <v>192.5</v>
       </c>
       <c r="E533" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>5</v>
       </c>
@@ -11882,13 +11876,13 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>187.5</v>
+        <v>195</v>
       </c>
       <c r="E534" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>5</v>
       </c>
@@ -11899,13 +11893,13 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>185</v>
+        <v>187.5</v>
       </c>
       <c r="E535" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>5</v>
       </c>
@@ -11916,13 +11910,13 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E536" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>5</v>
       </c>
@@ -11933,13 +11927,13 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>192.5</v>
+        <v>180</v>
       </c>
       <c r="E537" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>5</v>
       </c>
@@ -11950,13 +11944,13 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>197.5</v>
+        <v>192.5</v>
       </c>
       <c r="E538" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>5</v>
       </c>
@@ -11967,13 +11961,13 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>210</v>
+        <v>197.5</v>
       </c>
       <c r="E539" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>5</v>
       </c>
@@ -11990,7 +11984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>5</v>
       </c>
@@ -12001,13 +11995,13 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>213.5</v>
+        <v>210</v>
       </c>
       <c r="E541" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>5</v>
       </c>
@@ -12018,13 +12012,13 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>215</v>
+        <v>213.5</v>
       </c>
       <c r="E542" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -12035,13 +12029,13 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E543" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>5</v>
       </c>
@@ -12058,7 +12052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>5</v>
       </c>
@@ -12069,13 +12063,13 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E545" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>5</v>
       </c>
@@ -12092,7 +12086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>5</v>
       </c>
@@ -12103,13 +12097,13 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E547" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>5</v>
       </c>
@@ -12120,13 +12114,13 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E548" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>5</v>
       </c>
@@ -12137,13 +12131,13 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E549" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>5</v>
       </c>
@@ -12154,13 +12148,13 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>182.5</v>
+        <v>195</v>
       </c>
       <c r="E550" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>5</v>
       </c>
@@ -12171,13 +12165,13 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>177.5</v>
+        <v>182.5</v>
       </c>
       <c r="E551" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>5</v>
       </c>
@@ -12188,13 +12182,13 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>176.5</v>
+        <v>177.5</v>
       </c>
       <c r="E552" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>5</v>
       </c>
@@ -12211,7 +12205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>5</v>
       </c>
@@ -12222,13 +12216,13 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>172.5</v>
+        <v>176.5</v>
       </c>
       <c r="E554" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>5</v>
       </c>
@@ -12239,13 +12233,13 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>176.5</v>
+        <v>172.5</v>
       </c>
       <c r="E555" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>5</v>
       </c>
@@ -12256,13 +12250,13 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>175</v>
+        <v>176.5</v>
       </c>
       <c r="E556" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>5</v>
       </c>
@@ -12273,13 +12267,13 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E557" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>5</v>
       </c>
@@ -12290,13 +12284,13 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>167.5</v>
+        <v>170</v>
       </c>
       <c r="E558" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>5</v>
       </c>
@@ -12307,13 +12301,13 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>165</v>
+        <v>167.5</v>
       </c>
       <c r="E559" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>5</v>
       </c>
@@ -12330,7 +12324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>5</v>
       </c>
@@ -12341,13 +12335,13 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>167.5</v>
+        <v>165</v>
       </c>
       <c r="E561" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>5</v>
       </c>
@@ -12364,7 +12358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>5</v>
       </c>
@@ -12375,13 +12369,13 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>162.5</v>
+        <v>167.5</v>
       </c>
       <c r="E563" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>5</v>
       </c>
@@ -12392,13 +12386,13 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>170</v>
+        <v>162.5</v>
       </c>
       <c r="E564" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>5</v>
       </c>
@@ -12409,13 +12403,13 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>172.5</v>
+        <v>170</v>
       </c>
       <c r="E565" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>5</v>
       </c>
@@ -12426,13 +12420,13 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="E566" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>5</v>
       </c>
@@ -12443,13 +12437,13 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E567" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>5</v>
       </c>
@@ -12466,7 +12460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>5</v>
       </c>
@@ -12483,7 +12477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>5</v>
       </c>
@@ -12500,7 +12494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>5</v>
       </c>
@@ -12517,7 +12511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>5</v>
       </c>
@@ -12528,13 +12522,13 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>182.5</v>
+        <v>180</v>
       </c>
       <c r="E572" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>5</v>
       </c>
@@ -12545,13 +12539,13 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>177.5</v>
+        <v>182.5</v>
       </c>
       <c r="E573" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>5</v>
       </c>
@@ -12562,13 +12556,13 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>175</v>
+        <v>177.5</v>
       </c>
       <c r="E574" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>5</v>
       </c>
@@ -12579,13 +12573,13 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>173.5</v>
+        <v>175</v>
       </c>
       <c r="E575" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>5</v>
       </c>
@@ -12596,13 +12590,13 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>170</v>
+        <v>173.5</v>
       </c>
       <c r="E576" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>5</v>
       </c>
@@ -12619,7 +12613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>5</v>
       </c>
@@ -12636,7 +12630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>5</v>
       </c>
@@ -12653,7 +12647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>5</v>
       </c>
@@ -12670,7 +12664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>5</v>
       </c>
@@ -12687,7 +12681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>5</v>
       </c>
@@ -12704,7 +12698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>5</v>
       </c>
@@ -12721,7 +12715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>5</v>
       </c>
@@ -12732,13 +12726,13 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E584" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>5</v>
       </c>
@@ -12755,7 +12749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>5</v>
       </c>
@@ -12772,7 +12766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>5</v>
       </c>
@@ -12783,13 +12777,13 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E587" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>5</v>
       </c>
@@ -12800,13 +12794,13 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E588" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>5</v>
       </c>
@@ -12823,7 +12817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>5</v>
       </c>
@@ -12834,13 +12828,13 @@
         <v>7</v>
       </c>
       <c r="D590">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E590" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>5</v>
       </c>
@@ -12857,7 +12851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>5</v>
       </c>
@@ -12868,13 +12862,13 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E592" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="593" spans="1:5">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>5</v>
       </c>
@@ -12891,7 +12885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="594" spans="1:5">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>5</v>
       </c>
@@ -12908,7 +12902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:5">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>5</v>
       </c>
@@ -12925,7 +12919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:5">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>5</v>
       </c>
@@ -12942,7 +12936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:5">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -12953,13 +12947,13 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E597" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="598" spans="1:5">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>5</v>
       </c>
@@ -12976,7 +12970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="599" spans="1:5">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>5</v>
       </c>
@@ -12993,7 +12987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="600" spans="1:5">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>5</v>
       </c>
@@ -13004,13 +12998,13 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E600" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="601" spans="1:5">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>5</v>
       </c>
@@ -13027,7 +13021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="602" spans="1:5">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>5</v>
       </c>
@@ -13044,7 +13038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="603" spans="1:5">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>5</v>
       </c>
@@ -13055,13 +13049,13 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>192.5</v>
+        <v>190</v>
       </c>
       <c r="E603" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="604" spans="1:5">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>5</v>
       </c>
@@ -13072,13 +13066,13 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>195</v>
+        <v>192.5</v>
       </c>
       <c r="E604" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="605" spans="1:5">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>5</v>
       </c>
@@ -13089,13 +13083,13 @@
         <v>7</v>
       </c>
       <c r="D605">
-        <v>198.5</v>
+        <v>195</v>
       </c>
       <c r="E605" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:5">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>5</v>
       </c>
@@ -13106,13 +13100,13 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>203</v>
+        <v>198.5</v>
       </c>
       <c r="E606" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="607" spans="1:5">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>5</v>
       </c>
@@ -13123,13 +13117,13 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E607" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="608" spans="1:5">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>5</v>
       </c>
@@ -13146,7 +13140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:5">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>5</v>
       </c>
@@ -13157,13 +13151,13 @@
         <v>7</v>
       </c>
       <c r="D609">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E609" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="610" spans="1:5">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>5</v>
       </c>
@@ -13180,7 +13174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:5">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>5</v>
       </c>
@@ -13197,7 +13191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:5">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>5</v>
       </c>
@@ -13208,13 +13202,13 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E612" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:5">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>5</v>
       </c>
@@ -13231,7 +13225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="614" spans="1:5">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>5</v>
       </c>
@@ -13248,7 +13242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="615" spans="1:5">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>5</v>
       </c>
@@ -13265,7 +13259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="616" spans="1:5">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>5</v>
       </c>
@@ -13276,13 +13270,13 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E616" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="617" spans="1:5">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>5</v>
       </c>
@@ -13299,7 +13293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="618" spans="1:5">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>5</v>
       </c>
@@ -13316,7 +13310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:5">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>5</v>
       </c>
@@ -13333,7 +13327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="620" spans="1:5">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>5</v>
       </c>
@@ -13350,7 +13344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:5">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>5</v>
       </c>
@@ -13361,13 +13355,13 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>222.5</v>
+        <v>225</v>
       </c>
       <c r="E621" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="622" spans="1:5">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>5</v>
       </c>
@@ -13378,13 +13372,13 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>217.5</v>
+        <v>222.5</v>
       </c>
       <c r="E622" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="623" spans="1:5">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>5</v>
       </c>
@@ -13401,7 +13395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="624" spans="1:5">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>5</v>
       </c>
@@ -13412,13 +13406,13 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>227.5</v>
+        <v>217.5</v>
       </c>
       <c r="E624" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:5">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>5</v>
       </c>
@@ -13435,7 +13429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="626" spans="1:5">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>5</v>
       </c>
@@ -13446,13 +13440,13 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>232.5</v>
+        <v>227.5</v>
       </c>
       <c r="E626" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:5">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>5</v>
       </c>
@@ -13469,7 +13463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:5">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>5</v>
       </c>
@@ -13486,7 +13480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:5">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>5</v>
       </c>
@@ -13503,7 +13497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:5">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>5</v>
       </c>
@@ -13514,13 +13508,13 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>238.5</v>
+        <v>232.5</v>
       </c>
       <c r="E630" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:5">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>5</v>
       </c>
@@ -13531,13 +13525,13 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>242</v>
+        <v>238.5</v>
       </c>
       <c r="E631" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="632" spans="1:5">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>5</v>
       </c>
@@ -13554,7 +13548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="633" spans="1:5">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>5</v>
       </c>
@@ -13565,13 +13559,13 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>242.5</v>
+        <v>242</v>
       </c>
       <c r="E633" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="634" spans="1:5">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>5</v>
       </c>
@@ -13588,7 +13582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="635" spans="1:5">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>5</v>
       </c>
@@ -13599,13 +13593,13 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>245</v>
+        <v>242.5</v>
       </c>
       <c r="E635" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="636" spans="1:5">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>5</v>
       </c>
@@ -13622,7 +13616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="637" spans="1:5">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>5</v>
       </c>
@@ -13639,7 +13633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:5">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>5</v>
       </c>
@@ -13656,7 +13650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="639" spans="1:5">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>5</v>
       </c>
@@ -13673,7 +13667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="640" spans="1:5">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>5</v>
       </c>
@@ -13684,13 +13678,13 @@
         <v>7</v>
       </c>
       <c r="D640">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E640" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="641" spans="1:5">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>5</v>
       </c>
@@ -13701,13 +13695,13 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>252.5</v>
+        <v>250</v>
       </c>
       <c r="E641" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="642" spans="1:5">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>5</v>
       </c>
@@ -13724,7 +13718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="643" spans="1:5">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>5</v>
       </c>
@@ -13735,13 +13729,13 @@
         <v>7</v>
       </c>
       <c r="D643">
-        <v>257.5</v>
+        <v>252.5</v>
       </c>
       <c r="E643" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="644" spans="1:5">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>5</v>
       </c>
@@ -13758,7 +13752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="645" spans="1:5">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>5</v>
       </c>
@@ -13775,7 +13769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="646" spans="1:5">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>5</v>
       </c>
@@ -13792,7 +13786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:5">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>5</v>
       </c>
@@ -13809,7 +13803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="648" spans="1:5">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>5</v>
       </c>
@@ -13826,7 +13820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="649" spans="1:5">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>5</v>
       </c>
@@ -13837,13 +13831,13 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>262.5</v>
+        <v>257.5</v>
       </c>
       <c r="E649" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="650" spans="1:5">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>5</v>
       </c>
@@ -13854,13 +13848,13 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>272.5</v>
+        <v>262.5</v>
       </c>
       <c r="E650" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="651" spans="1:5">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>5</v>
       </c>
@@ -13877,7 +13871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="652" spans="1:5">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>5</v>
       </c>
@@ -13894,7 +13888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:5">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>5</v>
       </c>
@@ -13905,13 +13899,13 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>277.5</v>
+        <v>272.5</v>
       </c>
       <c r="E653" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:5">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>5</v>
       </c>
@@ -13928,7 +13922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="1:5">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>5</v>
       </c>
@@ -13939,13 +13933,13 @@
         <v>7</v>
       </c>
       <c r="D655">
-        <v>282</v>
+        <v>277.5</v>
       </c>
       <c r="E655" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="656" spans="1:5">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>5</v>
       </c>
@@ -13956,13 +13950,13 @@
         <v>7</v>
       </c>
       <c r="D656">
-        <v>284.5</v>
+        <v>282</v>
       </c>
       <c r="E656" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:5">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>5</v>
       </c>
@@ -13979,7 +13973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:5">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>5</v>
       </c>
@@ -13996,7 +13990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:5">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>5</v>
       </c>
@@ -14013,7 +14007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:5">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>5</v>
       </c>
@@ -14024,13 +14018,13 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>280</v>
+        <v>284.5</v>
       </c>
       <c r="E660" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="661" spans="1:5">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>5</v>
       </c>
@@ -14047,7 +14041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:5">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>5</v>
       </c>
@@ -14064,7 +14058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="663" spans="1:5">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>5</v>
       </c>
@@ -14075,13 +14069,13 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E663" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="664" spans="1:5">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>5</v>
       </c>
@@ -14092,13 +14086,13 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E664" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:5">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>5</v>
       </c>
@@ -14115,7 +14109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="666" spans="1:5">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>5</v>
       </c>
@@ -14126,13 +14120,13 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>292.5</v>
+        <v>290</v>
       </c>
       <c r="E666" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="667" spans="1:5">
+    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>5</v>
       </c>
@@ -14143,13 +14137,13 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>287.5</v>
+        <v>292.5</v>
       </c>
       <c r="E667" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="668" spans="1:5">
+    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>5</v>
       </c>
@@ -14166,7 +14160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="669" spans="1:5">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>5</v>
       </c>
@@ -14177,13 +14171,13 @@
         <v>7</v>
       </c>
       <c r="D669">
-        <v>292.5</v>
+        <v>287.5</v>
       </c>
       <c r="E669" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="670" spans="1:5">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>5</v>
       </c>
@@ -14194,13 +14188,13 @@
         <v>7</v>
       </c>
       <c r="D670">
-        <v>295</v>
+        <v>292.5</v>
       </c>
       <c r="E670" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="671" spans="1:5">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>5</v>
       </c>
@@ -14211,13 +14205,13 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>287.5</v>
+        <v>295</v>
       </c>
       <c r="E671" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="672" spans="1:5">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>5</v>
       </c>
@@ -14228,13 +14222,13 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>305</v>
+        <v>287.5</v>
       </c>
       <c r="E672" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:5">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>5</v>
       </c>
@@ -14251,7 +14245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="674" spans="1:5">
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>5</v>
       </c>
@@ -14268,7 +14262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:5">
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>5</v>
       </c>
@@ -14285,7 +14279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:5">
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>5</v>
       </c>
@@ -14302,7 +14296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:5">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>5</v>
       </c>
@@ -14313,13 +14307,13 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E677" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="678" spans="1:5">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>5</v>
       </c>
@@ -14330,13 +14324,13 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>317.5</v>
+        <v>304</v>
       </c>
       <c r="E678" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="679" spans="1:5">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>5</v>
       </c>
@@ -14353,7 +14347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:5">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>5</v>
       </c>
@@ -14370,7 +14364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:5">
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>5</v>
       </c>
@@ -14381,13 +14375,13 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>285</v>
+        <v>317.5</v>
       </c>
       <c r="E681" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="682" spans="1:5">
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>5</v>
       </c>
@@ -14398,13 +14392,13 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="E682" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="683" spans="1:5">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>5</v>
       </c>
@@ -14421,7 +14415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="684" spans="1:5">
+    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>5</v>
       </c>
@@ -14432,13 +14426,13 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>317.5</v>
+        <v>320</v>
       </c>
       <c r="E684" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:5">
+    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>5</v>
       </c>
@@ -14455,7 +14449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="686" spans="1:5">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>5</v>
       </c>
@@ -14466,13 +14460,13 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>335</v>
+        <v>317.5</v>
       </c>
       <c r="E686" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:5">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>5</v>
       </c>
@@ -14489,7 +14483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="688" spans="1:5">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>5</v>
       </c>
@@ -14506,7 +14500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="689" spans="1:5">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>5</v>
       </c>
@@ -14523,7 +14517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="690" spans="1:5">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>5</v>
       </c>
@@ -14540,7 +14534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="691" spans="1:5">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>5</v>
       </c>
@@ -14557,7 +14551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="692" spans="1:5">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>5</v>
       </c>
@@ -14574,7 +14568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="693" spans="1:5">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>5</v>
       </c>
@@ -14585,13 +14579,13 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>337.5</v>
+        <v>335</v>
       </c>
       <c r="E693" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:5">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>5</v>
       </c>
@@ -14602,13 +14596,13 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>350</v>
+        <v>337.5</v>
       </c>
       <c r="E694" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:5">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>5</v>
       </c>
@@ -14625,7 +14619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:5">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>5</v>
       </c>
@@ -14642,7 +14636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="697" spans="1:5">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>5</v>
       </c>
@@ -14659,7 +14653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="698" spans="1:5">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>5</v>
       </c>
@@ -14676,7 +14670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="699" spans="1:5">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>5</v>
       </c>
@@ -14693,7 +14687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="700" spans="1:5">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>5</v>
       </c>
@@ -14704,13 +14698,13 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>352.5</v>
+        <v>350</v>
       </c>
       <c r="E700" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="701" spans="1:5">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>5</v>
       </c>
@@ -14727,7 +14721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:5">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>5</v>
       </c>
@@ -14744,7 +14738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="703" spans="1:5">
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>5</v>
       </c>
@@ -14761,7 +14755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="704" spans="1:5">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>5</v>
       </c>
@@ -14772,13 +14766,13 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>355</v>
+        <v>352.5</v>
       </c>
       <c r="E704" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="705" spans="1:5">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>5</v>
       </c>
@@ -14795,7 +14789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="706" spans="1:5">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>5</v>
       </c>
@@ -14812,7 +14806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="707" spans="1:5">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>5</v>
       </c>
@@ -14829,7 +14823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="708" spans="1:5">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>5</v>
       </c>
@@ -14846,7 +14840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="709" spans="1:5">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>5</v>
       </c>
@@ -14863,7 +14857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="710" spans="1:5">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>5</v>
       </c>
@@ -14874,13 +14868,13 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E710" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="711" spans="1:5">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>5</v>
       </c>
@@ -14897,7 +14891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="712" spans="1:5">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>5</v>
       </c>
@@ -14914,7 +14908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="713" spans="1:5">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>5</v>
       </c>
@@ -14931,7 +14925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="714" spans="1:5">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>5</v>
       </c>
@@ -14948,7 +14942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="715" spans="1:5">
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>5</v>
       </c>
@@ -14965,7 +14959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="716" spans="1:5">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>5</v>
       </c>
@@ -14982,7 +14976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="717" spans="1:5">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>5</v>
       </c>
@@ -14999,7 +14993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="718" spans="1:5">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>5</v>
       </c>
@@ -15016,7 +15010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="719" spans="1:5">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>5</v>
       </c>
@@ -15033,7 +15027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="720" spans="1:5">
+    <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>5</v>
       </c>
@@ -15044,13 +15038,13 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E720" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="721" spans="1:5">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>5</v>
       </c>
@@ -15061,13 +15055,13 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E721" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="722" spans="1:5">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>5</v>
       </c>
@@ -15078,13 +15072,13 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E722" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="723" spans="1:5">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>5</v>
       </c>
@@ -15095,13 +15089,13 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>372.5</v>
+        <v>374</v>
       </c>
       <c r="E723" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="724" spans="1:5">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>5</v>
       </c>
@@ -15112,13 +15106,13 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>370</v>
+        <v>372.5</v>
       </c>
       <c r="E724" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="725" spans="1:5">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>5</v>
       </c>
@@ -15129,13 +15123,13 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E725" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="726" spans="1:5">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>5</v>
       </c>
@@ -15146,13 +15140,13 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>361.5</v>
+        <v>365</v>
       </c>
       <c r="E726" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="727" spans="1:5">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>5</v>
       </c>
@@ -15163,13 +15157,13 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>363</v>
+        <v>361.5</v>
       </c>
       <c r="E727" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="728" spans="1:5">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>5</v>
       </c>
@@ -15180,13 +15174,13 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>365.5</v>
+        <v>363</v>
       </c>
       <c r="E728" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="729" spans="1:5">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>5</v>
       </c>
@@ -15197,13 +15191,13 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>367.5</v>
+        <v>365.5</v>
       </c>
       <c r="E729" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="730" spans="1:5">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>5</v>
       </c>
@@ -15214,13 +15208,13 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>366</v>
+        <v>367.5</v>
       </c>
       <c r="E730" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="731" spans="1:5">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>5</v>
       </c>
@@ -15231,13 +15225,13 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>368.5</v>
+        <v>366</v>
       </c>
       <c r="E731" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="732" spans="1:5">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>5</v>
       </c>
@@ -15248,13 +15242,13 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>369.5</v>
+        <v>368.5</v>
       </c>
       <c r="E732" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="733" spans="1:5">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>5</v>
       </c>
@@ -15265,13 +15259,13 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>372</v>
+        <v>369.5</v>
       </c>
       <c r="E733" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="734" spans="1:5">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>5</v>
       </c>
@@ -15282,13 +15276,13 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E734" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="735" spans="1:5">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>5</v>
       </c>
@@ -15299,13 +15293,13 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>378.5</v>
+        <v>377</v>
       </c>
       <c r="E735" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="736" spans="1:5">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>5</v>
       </c>
@@ -15316,13 +15310,13 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>381</v>
+        <v>378.5</v>
       </c>
       <c r="E736" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="737" spans="1:5">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>5</v>
       </c>
@@ -15333,13 +15327,13 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>383.5</v>
+        <v>381</v>
       </c>
       <c r="E737" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="738" spans="1:5">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>5</v>
       </c>
@@ -15350,13 +15344,13 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>387.5</v>
+        <v>383.5</v>
       </c>
       <c r="E738" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="739" spans="1:5">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>5</v>
       </c>
@@ -15367,13 +15361,13 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>390</v>
+        <v>387.5</v>
       </c>
       <c r="E739" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="740" spans="1:5">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>5</v>
       </c>
@@ -15384,13 +15378,13 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>387.5</v>
+        <v>390</v>
       </c>
       <c r="E740" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="741" spans="1:5">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>5</v>
       </c>
@@ -15401,13 +15395,13 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>390</v>
+        <v>387.5</v>
       </c>
       <c r="E741" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="742" spans="1:5">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>5</v>
       </c>
@@ -15418,13 +15412,13 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E742" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="743" spans="1:5">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>5</v>
       </c>
@@ -15435,13 +15429,13 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>402.5</v>
+        <v>400</v>
       </c>
       <c r="E743" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="744" spans="1:5">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>5</v>
       </c>
@@ -15452,13 +15446,13 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>407.5</v>
+        <v>402.5</v>
       </c>
       <c r="E744" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="745" spans="1:5">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>5</v>
       </c>
@@ -15469,13 +15463,13 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>410</v>
+        <v>407.5</v>
       </c>
       <c r="E745" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="746" spans="1:5">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>5</v>
       </c>
@@ -15486,13 +15480,13 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>412.5</v>
+        <v>410</v>
       </c>
       <c r="E746" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="747" spans="1:5">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>5</v>
       </c>
@@ -15503,13 +15497,13 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>417.5</v>
+        <v>412.5</v>
       </c>
       <c r="E747" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="748" spans="1:5">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>5</v>
       </c>
@@ -15520,13 +15514,13 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>407.5</v>
+        <v>417.5</v>
       </c>
       <c r="E748" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="749" spans="1:5">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>5</v>
       </c>
@@ -15537,13 +15531,13 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>398.5</v>
+        <v>407.5</v>
       </c>
       <c r="E749" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="750" spans="1:5">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>5</v>
       </c>
@@ -15554,13 +15548,13 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>395.5</v>
+        <v>398.5</v>
       </c>
       <c r="E750" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="751" spans="1:5">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>5</v>
       </c>
@@ -15571,13 +15565,13 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>392.5</v>
+        <v>395.5</v>
       </c>
       <c r="E751" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="752" spans="1:5">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>5</v>
       </c>
@@ -15588,13 +15582,13 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>390</v>
+        <v>392.5</v>
       </c>
       <c r="E752" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="753" spans="1:5">
+    <row r="753" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>5</v>
       </c>
@@ -15605,13 +15599,13 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E753" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="754" spans="1:5">
+    <row r="754" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>5</v>
       </c>
@@ -15622,13 +15616,13 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E754" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="755" spans="1:5">
+    <row r="755" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>5</v>
       </c>
@@ -15639,13 +15633,13 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E755" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="756" spans="1:5">
+    <row r="756" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>5</v>
       </c>
@@ -15656,13 +15650,13 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E756" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="757" spans="1:5">
+    <row r="757" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>5</v>
       </c>
@@ -15673,13 +15667,13 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>351.5</v>
+        <v>360</v>
       </c>
       <c r="E757" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="758" spans="1:5">
+    <row r="758" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>5</v>
       </c>
@@ -15690,13 +15684,13 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>350</v>
+        <v>351.5</v>
       </c>
       <c r="E758" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="759" spans="1:5">
+    <row r="759" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>5</v>
       </c>
@@ -15707,13 +15701,13 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E759" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="760" spans="1:5">
+    <row r="760" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>5</v>
       </c>
@@ -15724,13 +15718,13 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E760" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="761" spans="1:5">
+    <row r="761" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>5</v>
       </c>
@@ -15741,13 +15735,13 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>332.5</v>
+        <v>339</v>
       </c>
       <c r="E761" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="762" spans="1:5">
+    <row r="762" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>5</v>
       </c>
@@ -15758,13 +15752,13 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>317.5</v>
+        <v>332.5</v>
       </c>
       <c r="E762" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="763" spans="1:5">
+    <row r="763" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>5</v>
       </c>
@@ -15775,13 +15769,13 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>310</v>
+        <v>317.5</v>
       </c>
       <c r="E763" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="764" spans="1:5">
+    <row r="764" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>5</v>
       </c>
@@ -15792,13 +15786,13 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E764" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="765" spans="1:5">
+    <row r="765" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>5</v>
       </c>
@@ -15809,13 +15803,13 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>297.5</v>
+        <v>300</v>
       </c>
       <c r="E765" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="766" spans="1:5">
+    <row r="766" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>5</v>
       </c>
@@ -15826,13 +15820,13 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>295</v>
+        <v>297.5</v>
       </c>
       <c r="E766" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="767" spans="1:5">
+    <row r="767" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>5</v>
       </c>
@@ -15843,13 +15837,13 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>307.5</v>
+        <v>295</v>
       </c>
       <c r="E767" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="768" spans="1:5">
+    <row r="768" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>5</v>
       </c>
@@ -15860,13 +15854,13 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>320</v>
+        <v>307.5</v>
       </c>
       <c r="E768" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="769" spans="1:5">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>5</v>
       </c>
@@ -15877,13 +15871,13 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E769" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="770" spans="1:5">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>5</v>
       </c>
@@ -15894,13 +15888,13 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E770" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="771" spans="1:5">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>5</v>
       </c>
@@ -15911,13 +15905,13 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="E771" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="772" spans="1:5">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>5</v>
       </c>
@@ -15928,13 +15922,13 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="E772" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="773" spans="1:5">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>5</v>
       </c>
@@ -15945,13 +15939,13 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E773" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="774" spans="1:5">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>5</v>
       </c>
@@ -15962,13 +15956,13 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E774" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="775" spans="1:5">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>5</v>
       </c>
@@ -15979,13 +15973,13 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E775" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="776" spans="1:5">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>5</v>
       </c>
@@ -15996,13 +15990,13 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E776" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="777" spans="1:5">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>5</v>
       </c>
@@ -16013,13 +16007,13 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E777" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="778" spans="1:5">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>5</v>
       </c>
@@ -16030,13 +16024,13 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>402.5</v>
+        <v>395</v>
       </c>
       <c r="E778" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="779" spans="1:5">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>5</v>
       </c>
@@ -16047,13 +16041,13 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>400</v>
+        <v>402.5</v>
       </c>
       <c r="E779" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="780" spans="1:5">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>5</v>
       </c>
@@ -16064,13 +16058,13 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E780" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="781" spans="1:5">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>5</v>
       </c>
@@ -16081,13 +16075,13 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>372.5</v>
+        <v>390</v>
       </c>
       <c r="E781" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="782" spans="1:5">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>5</v>
       </c>
@@ -16098,13 +16092,13 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>392.5</v>
+        <v>372.5</v>
       </c>
       <c r="E782" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="783" spans="1:5">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>5</v>
       </c>
@@ -16115,9 +16109,26 @@
         <v>7</v>
       </c>
       <c r="D783">
+        <v>392.5</v>
+      </c>
+      <c r="E783" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>5</v>
+      </c>
+      <c r="B784" t="s">
+        <v>788</v>
+      </c>
+      <c r="C784" t="s">
+        <v>7</v>
+      </c>
+      <c r="D784">
         <v>395</v>
       </c>
-      <c r="E783" t="s">
+      <c r="E784" t="s">
         <v>5</v>
       </c>
     </row>
